--- a/dashboard/assets/data_glossary.xlsx
+++ b/dashboard/assets/data_glossary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ashtiani\Desktop\WBLCA_Benchmarking\Material Intensity - Publication\GitHub - WORK ON THIS TILL FINAL\dashboard\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github repositories\Wedge\wblca-benchmark-v2-material-use-intensity\dashboard\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92299559-AB39-4DAE-9AB2-4977A3AF3F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48920AC2-4E7B-4E64-BEF4-BA07A41A422C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2061,7 +2061,7 @@
         <v>122</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2078,7 +2078,7 @@
         <v>121</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
